--- a/data/daily/2026-10/2026-10-14.xlsx
+++ b/data/daily/2026-10/2026-10-14.xlsx
@@ -1170,14 +1170,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1242,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1292,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,77 +1425,177 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,24 +1603,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1628,29 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,24 +2596,12 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16267</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>피로 회복 체감 — 시험기간이나 피곤한 날 섭취 시 확실히 피로가 덜하고 활력에 도움됨</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>선물용으로 적합 — 고급 비타민 이미지와 깔끔한 패키지로 생일 및 응원 선물로 만족도 높음</t>
-        </is>
-      </c>
+        <v>16270</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>소비기한 아쉬움 — 전체 소비기한 대비 이미 긴 기간이 경과한 재고성 상품을 수령하여 실망함</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -2648,35 +2636,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928083126_044ba1b10db84ccca43ebf7477214cc6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261014103242_f88fda29ab714a8b85e0d3e6699f6e32.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15605</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>간편한 복합 제형 — 상단 정제와 하단 액상이 함께 있어 물 없이도 언제 어디서나 섭취 편리함</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>피로감 개선 — 기력 저하나 피곤할 때 꾸준히 섭취 시 피로 완화에 효과를 느낌</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 깔끔하고 세련된 박스 패키지로 지인 및 가족 선물용으로 선호됨</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>배송 서비스 아쉬움 — 상품 자체는 만족스러우나 배송 측면에서 아쉬움이 남음</t>
-        </is>
-      </c>
+        <v>15607</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2720,21 +2692,9 @@
       <c r="J4" t="n">
         <v>3402</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>체력 및 활력 개선 — 환절기나 피로 누적 시 복용하면 다음 날 활력이 생기고 피로가 덜함</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>진한 액상 제형 — 타사 액상 비타민에 비해 농도가 진하여 섭취 만족감이 높음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 포장 — 배송이 빠르고 꼼꼼하게 포장되어 선물용으로 매우 유용함</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2779,21 +2739,9 @@
       <c r="J5" t="n">
         <v>6516</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 맛이라 간식처럼 부담 없이 즐김</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>간편한 섭취 방식 — 알약을 잘 넘기지 못하는 사람도 물 없이 편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>부담 없는 선물 — 예쁜 선물 포장과 귀여운 사은품으로 가볍게 선물하기 좋음</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2836,23 +2784,11 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>825</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>빠른 피로 완화 — 복용 며칠 만에 오후 시간대 체력 저하와 피로감이 확연히 줄어듦</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>뛰어난 휴대성 — 개별 포장이 견고하여 출근길이나 야외 활동 시 가방에 넣어 다니기 편리함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>물 없는 간편 섭취 — 액상과 정제가 결합되어 별도의 물 준비 없이 섭취 가능함</t>
-        </is>
-      </c>
+        <v>826</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2897,21 +2833,9 @@
       <c r="J7" t="n">
         <v>819</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>선물용 패키지 만족 — 포장이 정갈하고 예뻐 환절기나 생일 선물로 주고받기 좋음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>휴대 및 복용 편의 — 한 병씩 소포장되어 출근길이나 외출 시 챙겨 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>면역 및 활력 충전 — 환절기 체력 관리와 피로 완화용으로 믿고 섭취함</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2954,35 +2878,19 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>8749</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>다음 날 컨디션 개선 — 섭취 후 다음 날 피로가 덜하고 몸이 한결 가벼워짐을 체감함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>휴대 및 섭취 간편 — 정제와 액상이 세트로 구성되어 휴대하기 좋고 물 없이 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>부담 없는 맛 — 액상의 맛이 역하지 않고 거부감이 적어 꾸준히 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>소포장 볼륨감 아쉬움 — 소포장 구성 특성상 외관상 풍성해 보이지는 않는다는 의견 있음</t>
-        </is>
-      </c>
+        <v>8750</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2990,50 +2898,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>783</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>성별 맞춤형 구성 — 남성과 여성용 옵션이 나뉘어 있어 대상에 맞게 챙겨주기 좋음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>쓴맛 없는 복용감 — 비타민 특유의 쓴맛이 적고 진득하여 목넘김이 편함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>높은 피로 회복감 — 직장인 필수 영양제로 섭취 후 활력 증진에 큰 도움이 됨</t>
-        </is>
-      </c>
+        <v>1763</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -3041,7 +2937,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3049,55 +2945,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35,000원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1763</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>신선한 혼합 방식 — 캡을 눌러 분말을 액상에 터뜨려 즉석에서 신선하게 섞어 마심</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>빠른 기력 회복 — 음용 후 빠르게 활력이 충전되고 피로감이 개선되는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 각 잡힌 패키지와 쇼핑백 동봉으로 격식 있는 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>목넘김 후 텁텁함 — 분말 혼합 제형이라 약간 목이 메여 물을 추가로 마시게 됨</t>
-        </is>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3141,26 +3021,10 @@
       <c r="J11" t="n">
         <v>957</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>고함량 비타민 효과 — 매일 섭취 시 피부 상태나 피로 회복 등 컨디션 유지에 확실히 도움됨</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>넉넉한 대용량 구성 — 100포의 풍부한 용량으로 매일 꾸준히 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>선물 호불호 없음 — 남녀노소 무난하게 섭취하기 좋아 선물용으로 안성맞춤임</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>강한 신맛 — 고함량 분말 형태 특성상 신맛이 매우 강하게 느껴짐</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3202,23 +3066,11 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1697</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>편안한 소화감 — 식후 섭취 시 속 더부룩함이 덜하고 편안해짐을 느낌</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>풍성한 증정 혜택 — 할인 혜택과 더불어 단백질바, 추가 포 등 사은품 구성이 푸짐함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 포장 — 포장이 정성스럽고 깔끔하여 본인 및 지인 선물용으로 적합함</t>
-        </is>
-      </c>
+        <v>1700</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3234,7 +3086,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3244,56 +3096,36 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>23,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261013104549_cfa2b37d84e542f19a82e0967319903c.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>245</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>고소하고 상큼한 맛 — 상큼하면서도 고소하고 달콤하여 거부감 없이 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>아이돌 협업 디자인 — 아이돌 에디션 패키지 디자인이 예쁘고 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>물 없는 복용 편의 — 입안에서 잘 녹아 물 없이도 간편하게 섭취할 수 있음</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>적은 용량 대비 아쉬움 — 맛과 편의성은 좋으나 전체적인 양이 다소 적게 느껴짐</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>쇼핑백 규격 불편 — 동봉된 종이가방에 제품을 전부 넣기에 크기가 빡빡함</t>
-        </is>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3301,50 +3133,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>68</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>부드럽고 촉촉한 육질 — 닭가슴살 특유의 퍽퍽함 없이 매우 촉촉하여 식감이 우수함</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>다양하고 맛있는 양념 — 떡볶이맛 등 질리지 않는 다양한 소스 구성으로 맛있게 식단 관리 가능함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>간편한 조리법 — 전자레인지로 빠르고 간단하게 데워 먹을 수 있어 식사 대용으로 좋음</t>
-        </is>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -3352,7 +3172,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3360,55 +3180,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+파로저당견과류바 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261013104549_cfa2b37d84e542f19a82e0967319903c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>908</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>속 편한 소화 촉진 — 섭취 후 속 더부룩함이 완화되고 소화와 배변 활동에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>달콤한 옥수수맛 — 콘스프처럼 달달하고 고소하여 매일 거부감 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>알찬 사은품 증정 — 저당단백칩, 견과류바 등 유용한 사은품이 동봉되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>기존 대비 맛 차이 — 이전 구매 제품과 비교했을 때 맛의 차이가 느껴진다는 의견 있음</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -3452,26 +3256,10 @@
       <c r="J16" t="n">
         <v>755</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>고급스러운 오간자 패키지 — 포장과 가방 구성이 매우 세련되어 선물 개봉 시 만족도가 큼</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>맛있는 앰플 제형 — 비린맛 없이 맛이 좋아 하루 한 병씩 부담 없이 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>간편한 뷰티 케어 — 피부 탄력과 피로 관리를 마시는 형태로 손쉽게 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>다소 비싼 가격대 — 정가 기준 가격대가 높아 할인 프로모션 시에만 재구매하기 적합함</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -3513,28 +3301,12 @@
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>30</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>뛰어난 숙취 완화 — 음주 전후 섭취 시 다음 날 두통과 속 더부룩함이 줄어들고 개운함</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>휴대하기 좋은 스틱 — 소포장 액상 스틱 형태라 주머니나 가방에 넣어 물 없이 바로 짜 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>센스 있는 선물용 — 연말이나 잦은 회식 자리에 지인들에게 부담 없이 나눠주기 좋음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>한약 맛에 대한 호불호 — 약재 성분으로 인해 한약 특유의 짙은 향과 맛이 남</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3578,36 +3350,12 @@
       <c r="J18" t="n">
         <v>155</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>든든한 한 끼 포만감 — 한 팩만 섭취해도 포만감이 오래 지속되어 다이어트 식단용으로 우수함</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>맛있는 소스 구성 — 카레, 떡볶이 등 소스가 맛있어 닭가슴살을 질리지 않고 섭취함</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>합리적인 가성비 — 할인 프로모션 및 보냉백 증정 구성으로 대량 구매하기 적합함</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>포장 불량 및 터짐 — 진공 압착이 불량하거나 비닐이 터져 소스가 새어 나오는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>다소 강한 간 — 단독으로 먹기에는 간이 다소 세서 밥과 함께 먹어야 어울림</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>오배송 및 문의 지연 — 정해진 맛 구성이 아닌 임의 중복 배송이 발생하고 고객 응대가 늦음</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
@@ -3647,23 +3395,11 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1923</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>운동 수행 능력 향상 — 다이어트 중에도 세트 후반까지 반복 횟수와 근력을 유지하는 데 기여함</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>물에 잘 녹는 풀림성 — 찬물에도 뭉침 없이 잘 섞여 섭취 편의성이 뛰어남</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>믿을 수 있는 품질 — 특유의 거부감이나 불쾌한 맛 없이 깔끔하여 헬스 필수템으로 선호됨</t>
-        </is>
-      </c>
+        <v>1925</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3706,28 +3442,12 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1190</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>음료 같은 우수한 맛 — 알로에, 청포도, 매실 등 음료처럼 상큼달콤하여 맹물 대신 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>부드러운 용해력 — 찬물에도 가루가 잘 풀려 운동 중 수분 보충용으로 제격임</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>운동 중 속 편안함 — 운동 중 마셔도 속이 더부룩하지 않고 활력 충전에 도움됨</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>직접 구매 시 가격 부담 — 정가 구매 기준 가격대가 다소 높아 선물용이 아닐 시 부담스러울 수 있음</t>
-        </is>
-      </c>
+        <v>1191</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3771,26 +3491,10 @@
       <c r="J21" t="n">
         <v>1535</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>복합 성분의 시너지 — 활력을 위한 아르기닌과 간 건강을 위한 밀크씨슬/마카를 한 번에 관리함</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>아침 피로 완화 — 꾸준히 섭취 시 아침 기상이 한결 가볍고 일상 활력이 눈에 띄게 개선됨</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>고급 선물 패키지 — 2개월분의 넉넉한 양과 전용 쇼핑백 동봉으로 선물 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>쇼핑백 마감 불량 — 선물용으로 동봉된 전용 쇼핑백의 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3940,12 +3644,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3997,12 +3701,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -4054,12 +3758,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -4112,10 +3816,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16267</v>
+        <v>16270</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15605</v>
+        <v>15607</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3402</v>
@@ -4124,99 +3828,40 @@
         <v>6516</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>819</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8749</v>
+        <v>8750</v>
       </c>
       <c r="J7" s="3" t="n">
+        <v>1763</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>783</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>1763</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>957</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>피로 회복 체감 — 시험기간이나 피곤한 날 섭취 시 확실히 피로가 덜하고 활력에 도움됨
-선물용으로 적합 — 고급 비타민 이미지와 깔끔한 패키지로 생일 및 응원 선물로 만족도 높음</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 복합 제형 — 상단 정제와 하단 액상이 함께 있어 물 없이도 언제 어디서나 섭취 편리함
-피로감 개선 — 기력 저하나 피곤할 때 꾸준히 섭취 시 피로 완화에 효과를 느낌
-고급스러운 포장 — 깔끔하고 세련된 박스 패키지로 지인 및 가족 선물용으로 선호됨</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>체력 및 활력 개선 — 환절기나 피로 누적 시 복용하면 다음 날 활력이 생기고 피로가 덜함
-진한 액상 제형 — 타사 액상 비타민에 비해 농도가 진하여 섭취 만족감이 높음
-빠른 배송 및 포장 — 배송이 빠르고 꼼꼼하게 포장되어 선물용으로 매우 유용함</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 맛이라 간식처럼 부담 없이 즐김
-간편한 섭취 방식 — 알약을 잘 넘기지 못하는 사람도 물 없이 편하게 섭취 가능함
-부담 없는 선물 — 예쁜 선물 포장과 귀여운 사은품으로 가볍게 선물하기 좋음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 피로 완화 — 복용 며칠 만에 오후 시간대 체력 저하와 피로감이 확연히 줄어듦
-뛰어난 휴대성 — 개별 포장이 견고하여 출근길이나 야외 활동 시 가방에 넣어 다니기 편리함
-물 없는 간편 섭취 — 액상과 정제가 결합되어 별도의 물 준비 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>선물용 패키지 만족 — 포장이 정갈하고 예뻐 환절기나 생일 선물로 주고받기 좋음
-휴대 및 복용 편의 — 한 병씩 소포장되어 출근길이나 외출 시 챙겨 먹기 수월함
-면역 및 활력 충전 — 환절기 체력 관리와 피로 완화용으로 믿고 섭취함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>다음 날 컨디션 개선 — 섭취 후 다음 날 피로가 덜하고 몸이 한결 가벼워짐을 체감함
-휴대 및 섭취 간편 — 정제와 액상이 세트로 구성되어 휴대하기 좋고 물 없이 복용 가능함
-부담 없는 맛 — 액상의 맛이 역하지 않고 거부감이 적어 꾸준히 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>성별 맞춤형 구성 — 남성과 여성용 옵션이 나뉘어 있어 대상에 맞게 챙겨주기 좋음
-쓴맛 없는 복용감 — 비타민 특유의 쓴맛이 적고 진득하여 목넘김이 편함
-높은 피로 회복감 — 직장인 필수 영양제로 섭취 후 활력 증진에 큰 도움이 됨</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>신선한 혼합 방식 — 캡을 눌러 분말을 액상에 터뜨려 즉석에서 신선하게 섞어 마심
-빠른 기력 회복 — 음용 후 빠르게 활력이 충전되고 피로감이 개선되는 느낌을 받음
-고급스러운 포장 — 각 잡힌 패키지와 쇼핑백 동봉으로 격식 있는 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>고함량 비타민 효과 — 매일 섭취 시 피부 상태나 피로 회복 등 컨디션 유지에 확실히 도움됨
-넉넉한 대용량 구성 — 100포의 풍부한 용량으로 매일 꾸준히 챙겨 먹기 적합함
-선물 호불호 없음 — 남녀노소 무난하게 섭취하기 좋아 선물용으로 안성맞춤임</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -4224,36 +3869,16 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>소비기한 아쉬움 — 전체 소비기한 대비 이미 긴 기간이 경과한 재고성 상품을 수령하여 실망함</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>배송 서비스 아쉬움 — 상품 자체는 만족스러우나 배송 측면에서 아쉬움이 남음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>소포장 볼륨감 아쉬움 — 소포장 구성 특성상 외관상 풍성해 보이지는 않는다는 의견 있음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>목넘김 후 텁텁함 — 분말 혼합 제형이라 약간 목이 메여 물을 추가로 마시게 됨</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛 — 고함량 분말 형태 특성상 신맛이 매우 강하게 느껴짐</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4298,12 +3923,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>59,800원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>35,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -4461,12 +4086,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4518,12 +4143,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -4570,17 +4195,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+파로저당견과류바 증정</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4658,160 +4283,69 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>245</v>
+        <v>908</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>68</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>908</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>755</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>155</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>1535</v>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>편안한 소화감 — 식후 섭취 시 속 더부룩함이 덜하고 편안해짐을 느낌
-풍성한 증정 혜택 — 할인 혜택과 더불어 단백질바, 추가 포 등 사은품 구성이 푸짐함
-고급스러운 선물 포장 — 포장이 정성스럽고 깔끔하여 본인 및 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>고소하고 상큼한 맛 — 상큼하면서도 고소하고 달콤하여 거부감 없이 맛있게 먹기 좋음
-아이돌 협업 디자인 — 아이돌 에디션 패키지 디자인이 예쁘고 소장 가치가 높음
-물 없는 복용 편의 — 입안에서 잘 녹아 물 없이도 간편하게 섭취할 수 있음</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>부드럽고 촉촉한 육질 — 닭가슴살 특유의 퍽퍽함 없이 매우 촉촉하여 식감이 우수함
-다양하고 맛있는 양념 — 떡볶이맛 등 질리지 않는 다양한 소스 구성으로 맛있게 식단 관리 가능함
-간편한 조리법 — 전자레인지로 빠르고 간단하게 데워 먹을 수 있어 식사 대용으로 좋음</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>속 편한 소화 촉진 — 섭취 후 속 더부룩함이 완화되고 소화와 배변 활동에 도움이 됨
-달콤한 옥수수맛 — 콘스프처럼 달달하고 고소하여 매일 거부감 없이 섭취 가능함
-알찬 사은품 증정 — 저당단백칩, 견과류바 등 유용한 사은품이 동봉되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 오간자 패키지 — 포장과 가방 구성이 매우 세련되어 선물 개봉 시 만족도가 큼
-맛있는 앰플 제형 — 비린맛 없이 맛이 좋아 하루 한 병씩 부담 없이 마시기 좋음
-간편한 뷰티 케어 — 피부 탄력과 피로 관리를 마시는 형태로 손쉽게 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 숙취 완화 — 음주 전후 섭취 시 다음 날 두통과 속 더부룩함이 줄어들고 개운함
-휴대하기 좋은 스틱 — 소포장 액상 스틱 형태라 주머니나 가방에 넣어 물 없이 바로 짜 먹기 편함
-센스 있는 선물용 — 연말이나 잦은 회식 자리에 지인들에게 부담 없이 나눠주기 좋음</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>든든한 한 끼 포만감 — 한 팩만 섭취해도 포만감이 오래 지속되어 다이어트 식단용으로 우수함
-맛있는 소스 구성 — 카레, 떡볶이 등 소스가 맛있어 닭가슴살을 질리지 않고 섭취함
-합리적인 가성비 — 할인 프로모션 및 보냉백 증정 구성으로 대량 구매하기 적합함</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>운동 수행 능력 향상 — 다이어트 중에도 세트 후반까지 반복 횟수와 근력을 유지하는 데 기여함
-물에 잘 녹는 풀림성 — 찬물에도 뭉침 없이 잘 섞여 섭취 편의성이 뛰어남
-믿을 수 있는 품질 — 특유의 거부감이나 불쾌한 맛 없이 깔끔하여 헬스 필수템으로 선호됨</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>음료 같은 우수한 맛 — 알로에, 청포도, 매실 등 음료처럼 상큼달콤하여 맹물 대신 마시기 좋음
-부드러운 용해력 — 찬물에도 가루가 잘 풀려 운동 중 수분 보충용으로 제격임
-운동 중 속 편안함 — 운동 중 마셔도 속이 더부룩하지 않고 활력 충전에 도움됨</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>복합 성분의 시너지 — 활력을 위한 아르기닌과 간 건강을 위한 밀크씨슬/마카를 한 번에 관리함
-아침 피로 완화 — 꾸준히 섭취 시 아침 기상이 한결 가볍고 일상 활력이 눈에 띄게 개선됨
-고급 선물 패키지 — 2개월분의 넉넉한 양과 전용 쇼핑백 동봉으로 선물 만족도가 높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>적은 용량 대비 아쉬움 — 맛과 편의성은 좋으나 전체적인 양이 다소 적게 느껴짐
-쇼핑백 규격 불편 — 동봉된 종이가방에 제품을 전부 넣기에 크기가 빡빡함</t>
-        </is>
-      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>기존 대비 맛 차이 — 이전 구매 제품과 비교했을 때 맛의 차이가 느껴진다는 의견 있음</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>다소 비싼 가격대 — 정가 기준 가격대가 높아 할인 프로모션 시에만 재구매하기 적합함</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>한약 맛에 대한 호불호 — 약재 성분으로 인해 한약 특유의 짙은 향과 맛이 남</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>포장 불량 및 터짐 — 진공 압착이 불량하거나 비닐이 터져 소스가 새어 나오는 경우가 있음
-다소 강한 간 — 단독으로 먹기에는 간이 다소 세서 밥과 함께 먹어야 어울림
-오배송 및 문의 지연 — 정해진 맛 구성이 아닌 임의 중복 배송이 발생하고 고객 응대가 늦음</t>
-        </is>
-      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>직접 구매 시 가격 부담 — 정가 구매 기준 가격대가 다소 높아 선물용이 아닐 시 부담스러울 수 있음</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 마감 불량 — 선물용으로 동봉된 전용 쇼핑백의 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4826,17 +4360,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>23,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>33,000원</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>23,900원</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -5056,7 +4590,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5064,58 +4598,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>872</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 소용량 단위로 저렴하게 구매하여 단기 활력 충전용으로 이용하기 좋음</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>빠른 기력 보충 — 운동이나 일상 중 섭취 시 활력이 돋고 힘이 나는 효과를 체감함</t>
-        </is>
-      </c>
+        <v>7297</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>진하고 강한 맛 — 농축된 액상 특유의 맛이 매우 진해 단독으로 삼키기 다소 부담스러움</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5123,12 +4645,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5138,36 +4660,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2299</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>채소 섭취 보완 — 평소 샐러드나 야채를 챙겨 먹기 힘든 사람들에게 유용한 간식 대용품임</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>간편한 섭취 방식 — 알갱이 볼 형태로 가볍게 집어 먹기 좋아 편의성이 높음</t>
-        </is>
-      </c>
+        <v>6871</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>단단한 식감 — 생각보다 제형이 단단하여 씹어 먹을 때 다소 딱딱하게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5182,51 +4692,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953530&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/j2jn8GpSpWpVPin1SKu2994953530_00_00j2jn8GpSpWpVPin1SKu2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>235</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>시원하고 맛있는 복용감 — 입안에 넣었을 때 청량한 쿨링감이 돌고 과하게 시지 않아 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>합리적인 가격 접근성 — 다이소에서 부담 없는 가격으로 이너뷰티 비타민을 가볍게 섭취함</t>
-        </is>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>효과 체감의 모호함 — 맛있는 분말 형태이나 단기 섭취 시 뚜렷한 기능적 효과 체감은 부족함</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5241,62 +4739,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>242</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>상쾌한 구강 청량감 — 레몬과 민트향이 어우러져 식후나 답답할 때 입안을 산뜻하게 정돈함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>편리한 휴대성 — 개별 PTP 포장으로 파우치나 가방에 휴대하여 필요할 때 꺼내 먹기 용이함</t>
-        </is>
-      </c>
+        <v>4070</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>캡슐 껍질의 이물감 — 씹어서 터뜨릴 때 남는 잔여 캡슐 피막이 목에 걸리는 느낌이 듦</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>짧은 상쾌함 지속력 — 순간적인 청량감은 좋으나 구취 케어 효과의 지속 시간이 짧음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5304,62 +4786,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>6715</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>비린내 없는 복용감 — 오메가3 특유의 어취가 거의 없어 거부감 없이 삼키기 수월함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>부담 없는 가성비 — 대웅제약 브랜드 제품을 한 달 단위로 저렴하게 복용할 수 있음</t>
-        </is>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>큰 캡슐 크기 — 알약 크기가 다소 큰 편이라 삼킬 때 목넘김에 주의가 필요함</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>다소 낮은 유효 함량 — 가격 대비 무난하지만 단일 캡슐당 영양소 함량 수치는 다소 낮음</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5367,12 +4833,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>안국약품 브이팩 남성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5382,30 +4848,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235547&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/jgM8z9lj7cP7W5etxeXM968235547_00_00jgM8z9lj7cP7W5etxeXM.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2895</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>속 쓰림 없는 정제 — 과도한 고함량이 아니라서 위가 약한 사람도 부담 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>우수한 가격 경쟁력 — 합리적인 가격대로 매일 꾸준히 재구매하여 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -5422,51 +4880,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1463</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>붓기 및 갈증 완화 — 짠 음식을 섭취한 후나 수분 보충 시 간편하게 마시기 유용함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>물 마시기 용이 — 맹물을 마시기 힘들어하는 사람도 상큼하게 수분을 섭취할 수 있음</t>
-        </is>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>다소 적은 포당 용량 — 물에 타 마시는 분말의 양과 팩당 구성 수량이 다소 적게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -5481,12 +4927,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5496,36 +4942,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>203</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>부모님 선물로 인기 — 정성스러운 한 알 패키지로 부모님이나 어르신 기력 보충용으로 선호됨</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>합리적인 가격의 침향 — 고가의 침향환을 저렴한 가격에 소량 단위로 체험 및 섭취 가능함</t>
-        </is>
-      </c>
+        <v>1466</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>한방 맛의 연령별 호불호 — 진한 한방 환 특유의 향미로 인해 젊은 층에서는 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5540,58 +4974,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910601&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250502/YBmj8aPscGIkmB6O6RuJ610910601_00_00YBmj8aPscGIkmB6O6RuJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>658</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>맛있고 간편한 섭취 — 거부감 없는 맛으로 매일 간편하게 털어 넣으며 피부 건강을 챙김</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>꾸준한 재구매율 — 저렴한 가격과 빠른 배송 덕분에 반복적으로 쟁여두고 복용함</t>
-        </is>
-      </c>
+        <v>3641</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>평이한 체감 효과 — 기대치에 비해 단기적인 신체 변화나 효능은 평범하다는 반응 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5599,12 +5021,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5614,30 +5036,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2964</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>극강의 가성비 — 5천 원대의 매우 저렴한 가격으로 한 달 분량의 유산균을 관리 가능함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>여성 맞춤형 설계 — 여성 건강에 맞춘 유산균 구성으로 꾸준히 섭취하기에 부담이 없음</t>
-        </is>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -5754,52 +5168,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -5811,52 +5225,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>이너뷰 바이 리튠</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
     </row>
@@ -5868,52 +5282,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>안국약품 브이팩 남성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
         </is>
       </c>
     </row>
@@ -5927,25 +5341,25 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>4.6</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
@@ -5961,152 +5375,68 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>872</v>
+        <v>7297</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2299</v>
+        <v>6871</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>242</v>
+        <v>4070</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6715</v>
+        <v>247</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2895</v>
+        <v>494</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1463</v>
+        <v>559</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>203</v>
+        <v>1466</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>658</v>
+        <v>3641</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2964</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 소용량 단위로 저렴하게 구매하여 단기 활력 충전용으로 이용하기 좋음
-빠른 기력 보충 — 운동이나 일상 중 섭취 시 활력이 돋고 힘이 나는 효과를 체감함</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>채소 섭취 보완 — 평소 샐러드나 야채를 챙겨 먹기 힘든 사람들에게 유용한 간식 대용품임
-간편한 섭취 방식 — 알갱이 볼 형태로 가볍게 집어 먹기 좋아 편의성이 높음</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>시원하고 맛있는 복용감 — 입안에 넣었을 때 청량한 쿨링감이 돌고 과하게 시지 않아 먹기 좋음
-합리적인 가격 접근성 — 다이소에서 부담 없는 가격으로 이너뷰티 비타민을 가볍게 섭취함</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>상쾌한 구강 청량감 — 레몬과 민트향이 어우러져 식후나 답답할 때 입안을 산뜻하게 정돈함
-편리한 휴대성 — 개별 PTP 포장으로 파우치나 가방에 휴대하여 필요할 때 꺼내 먹기 용이함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>비린내 없는 복용감 — 오메가3 특유의 어취가 거의 없어 거부감 없이 삼키기 수월함
-부담 없는 가성비 — 대웅제약 브랜드 제품을 한 달 단위로 저렴하게 복용할 수 있음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>속 쓰림 없는 정제 — 과도한 고함량이 아니라서 위가 약한 사람도 부담 없이 섭취 가능함
-우수한 가격 경쟁력 — 합리적인 가격대로 매일 꾸준히 재구매하여 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>붓기 및 갈증 완화 — 짠 음식을 섭취한 후나 수분 보충 시 간편하게 마시기 유용함
-물 마시기 용이 — 맹물을 마시기 힘들어하는 사람도 상큼하게 수분을 섭취할 수 있음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>부모님 선물로 인기 — 정성스러운 한 알 패키지로 부모님이나 어르신 기력 보충용으로 선호됨
-합리적인 가격의 침향 — 고가의 침향환을 저렴한 가격에 소량 단위로 체험 및 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>맛있고 간편한 섭취 — 거부감 없는 맛으로 매일 간편하게 털어 넣으며 피부 건강을 챙김
-꾸준한 재구매율 — 저렴한 가격과 빠른 배송 덕분에 반복적으로 쟁여두고 복용함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>극강의 가성비 — 5천 원대의 매우 저렴한 가격으로 한 달 분량의 유산균을 관리 가능함
-여성 맞춤형 설계 — 여성 건강에 맞춘 유산균 구성으로 꾸준히 섭취하기에 부담이 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>진하고 강한 맛 — 농축된 액상 특유의 맛이 매우 진해 단독으로 삼키기 다소 부담스러움</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>단단한 식감 — 생각보다 제형이 단단하여 씹어 먹을 때 다소 딱딱하게 느껴짐</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 모호함 — 맛있는 분말 형태이나 단기 섭취 시 뚜렷한 기능적 효과 체감은 부족함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>캡슐 껍질의 이물감 — 씹어서 터뜨릴 때 남는 잔여 캡슐 피막이 목에 걸리는 느낌이 듦
-짧은 상쾌함 지속력 — 순간적인 청량감은 좋으나 구취 케어 효과의 지속 시간이 짧음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>큰 캡슐 크기 — 알약 크기가 다소 큰 편이라 삼킬 때 목넘김에 주의가 필요함
-다소 낮은 유효 함량 — 가격 대비 무난하지만 단일 캡슐당 영양소 함량 수치는 다소 낮음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>다소 적은 포당 용량 — 물에 타 마시는 분말의 양과 팩당 구성 수량이 다소 적게 느껴짐</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>한방 맛의 연령별 호불호 — 진한 한방 환 특유의 향미로 인해 젊은 층에서는 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>평이한 체감 효과 — 기대치에 비해 단기적인 신체 변화나 효능은 평범하다는 반응 있음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6117,7 +5447,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6127,37 +5457,37 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6341,7 +5671,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6349,27 +5679,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6427,7 +5757,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6435,27 +5765,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6470,7 +5800,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6478,27 +5808,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6521,7 +5851,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6531,17 +5861,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6556,7 +5886,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6564,27 +5894,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6599,7 +5929,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6607,55 +5937,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>세노비스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258054&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41382</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>확실한 피로 완화 — 피로 누적이나 여행 중 체력 저하 시 섭취하면 활력이 빠르게 회복됨</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>진한 액상 활용도 — 꾸덕하고 진한 비타민 액상을 탄산수나 물에 섞어 에이드처럼 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>다양한 캐릭터 협업 — 포차코 등 인기 캐릭터 콜라보 패키지와 사은품 증정으로 소장 가치 높음</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>높은 정가 가격대 — 품질과 효능은 우수하지만 타 비타민 대비 정가 기준 가격이 다소 비쌈</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025805404ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -6693,35 +6003,19 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587422ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5657</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 제형 — 간식 젤리처럼 새콤달콤하고 쫀득하여 영양제 복용 거부감이 전혀 없음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>물 없는 간편 섭취 — 차 안이나 바쁜 출퇴근 시간에도 물 없이 간편하게 씹어 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>취향에 따른 호불호 — 간식 같은 구미 제형 특성상 손이 잘 가지 않아 재구매를 망설인다는 의견 있음</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6729,51 +6023,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>27163</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>원활한 배변 활동 — 섭취 후 화장실을 수월하게 가게 되어 뱃살 및 잔여감 해소에 유용함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>귀여운 캐릭터 콜라보 — 헬로키티 등 아기자기한 콜라보 디자인으로 섭취 만족도를 더함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>큰 알약 크기 — 정제 크기가 다소 큰 편이라 목넘김 시 다소 부담스러울 수 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -6788,45 +6066,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17419</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>빠른 얼굴 붓기 완화 — 야식 섭취 후나 중요한 촬영 전 복용 시 얼굴 붓기 개선에 뛰어난 효과를 보임</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>간편한 미니환 제형 — 알갱이가 작은 환 형태라 큰 알약을 못 먹는 사람도 물과 함께 쉽게 삼킴</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6943,37 +6209,37 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -6983,7 +6249,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -7000,22 +6266,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -7025,12 +6291,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>세노비스</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -7040,12 +6306,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -7057,37 +6323,37 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -7097,12 +6363,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
     </row>
@@ -7118,18 +6384,10 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7143,20 +6401,12 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>41382</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>5657</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>27163</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>17419</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7168,31 +6418,10 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>확실한 피로 완화 — 피로 누적이나 여행 중 체력 저하 시 섭취하면 활력이 빠르게 회복됨
-진한 액상 활용도 — 꾸덕하고 진한 비타민 액상을 탄산수나 물에 섞어 에이드처럼 마시기 좋음
-다양한 캐릭터 협업 — 포차코 등 인기 캐릭터 콜라보 패키지와 사은품 증정으로 소장 가치 높음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 제형 — 간식 젤리처럼 새콤달콤하고 쫀득하여 영양제 복용 거부감이 전혀 없음
-물 없는 간편 섭취 — 차 안이나 바쁜 출퇴근 시간에도 물 없이 간편하게 씹어 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>원활한 배변 활동 — 섭취 후 화장실을 수월하게 가게 되어 뱃살 및 잔여감 해소에 유용함
-귀여운 캐릭터 콜라보 — 헬로키티 등 아기자기한 콜라보 디자인으로 섭취 만족도를 더함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 얼굴 붓기 완화 — 야식 섭취 후나 중요한 촬영 전 복용 시 얼굴 붓기 개선에 뛰어난 효과를 보임
-간편한 미니환 제형 — 알갱이가 작은 환 형태라 큰 알약을 못 먹는 사람도 물과 함께 쉽게 삼킴</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7206,21 +6435,9 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>높은 정가 가격대 — 품질과 효능은 우수하지만 타 비타민 대비 정가 기준 가격이 다소 비쌈</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>취향에 따른 호불호 — 간식 같은 구미 제형 특성상 손이 잘 가지 않아 재구매를 망설인다는 의견 있음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>큰 알약 크기 — 정제 크기가 다소 큰 편이라 목넘김 시 다소 부담스러울 수 있음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7231,37 +6448,37 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>61,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -7271,12 +6488,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>5,900원</t>
         </is>
       </c>
     </row>
@@ -7364,7 +6581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7406,10 +6623,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -7418,7 +6635,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -7437,10 +6654,10 @@
         <v>7</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -7450,19 +6667,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7472,16 +6689,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -7490,14 +6707,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -7506,13 +6723,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7522,19 +6739,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7556,7 +6773,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7566,12 +6783,56 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
